--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,7 +278,7 @@
 https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdm-actor-patienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdm-actor-snrhttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdm-actor-system</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée représente la personne physique ou le système émetteur du lot de soumission.Pour les documents d’expression personnelle du patient, cette métadonnée fait référence au patient.  </t>
+    <t>Cette métadonnée représente la personne physique ou le système émetteur du lot de soumission.Pour les documents d’expression personnelle du patient, cette métadonnée fait référence au patient.</t>
   </si>
   <si>
     <t>Author</t>
@@ -294,7 +294,7 @@
 </t>
   </si>
   <si>
-    <t>ette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
+    <t>Cette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
   </si>
   <si>
     <t>**Author Role**</t>
@@ -312,7 +312,7 @@
     <t>xdm-author-submission-set.specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente la profession éventuellement associée au savoir-faire de l’auteur professionnel caractérisé par sa profession ou la profession associée au genre d’activité pour l’auteur professionnel caractérisé par son rôle. </t>
+    <t>Cet attribut représente la profession éventuellement associée au savoir-faire de l’auteur professionnel caractérisé par sa profession ou la profession associée au genre d’activité pour l’auteur professionnel caractérisé par son rôle.</t>
   </si>
   <si>
     <t>**AutorSpecialty**</t>

--- a/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-author-submission-set.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
